--- a/docs/智诊通-项目计划.xlsx
+++ b/docs/智诊通-项目计划.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16100"/>
+    <workbookView windowHeight="21840"/>
   </bookViews>
   <sheets>
     <sheet name="项目计划" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="62">
   <si>
     <t>序号</t>
   </si>
@@ -51,7 +51,8 @@
     <t>第一阶段</t>
   </si>
   <si>
-    <t>推理模型(文本RAG系统)</t>
+    <t>推理模型
+(文本RAG系统)</t>
   </si>
   <si>
     <t>算法开发</t>
@@ -60,6 +61,9 @@
     <t>搭建LangChain开发环境</t>
   </si>
   <si>
+    <t>田库、臧昊、范金龙、杨玥</t>
+  </si>
+  <si>
     <t>2025/8/13-2025/8/22</t>
   </si>
   <si>
@@ -72,6 +76,9 @@
     <t>实现文本向量化</t>
   </si>
   <si>
+    <t>田库、朴明喆、刘书芹、刘毅军</t>
+  </si>
+  <si>
     <t>构建向量数据库</t>
   </si>
   <si>
@@ -84,6 +91,9 @@
     <t>实现API接口</t>
   </si>
   <si>
+    <t>张志良、焦志远、于洪胜、郭亮</t>
+  </si>
+  <si>
     <t>实现文本问答功能</t>
   </si>
   <si>
@@ -105,6 +115,9 @@
     <t>完成整个系统流程的初步测试，以可用为目标</t>
   </si>
   <si>
+    <t>张志良、焦志远、臧昊、刘毅军</t>
+  </si>
+  <si>
     <t>第二阶段</t>
   </si>
   <si>
@@ -114,6 +127,9 @@
     <t>优化RAG检索算法，优化检索效果</t>
   </si>
   <si>
+    <t>田库、张志良、焦志远、臧昊</t>
+  </si>
+  <si>
     <t>2025/8/22-2025/8/29</t>
   </si>
   <si>
@@ -132,6 +148,9 @@
     <t>实现用户会话管理</t>
   </si>
   <si>
+    <t>田库、张志良、柯华应、隋衡</t>
+  </si>
+  <si>
     <t>保存对话历史</t>
   </si>
   <si>
@@ -147,10 +166,14 @@
     <t>第三阶段</t>
   </si>
   <si>
-    <t>系统功能扩展（多模态整合）)</t>
+    <t>系统功能扩展
+（多模态整合）</t>
   </si>
   <si>
     <t>集成图像识别功能</t>
+  </si>
+  <si>
+    <t>张志良、焦志远、朴明喆、刘毅军</t>
   </si>
   <si>
     <t>2025/8/30-2025/9/5</t>
@@ -205,13 +228,20 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
     </font>
     <font>
       <u/>
@@ -730,133 +760,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -870,6 +900,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -878,15 +917,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1413,454 +1443,485 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F46"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <dimension ref="B2:H28"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="13.7788461538462" customWidth="1"/>
-    <col min="3" max="3" width="31.7211538461538" customWidth="1"/>
-    <col min="4" max="4" width="17.4615384615385" customWidth="1"/>
-    <col min="5" max="5" width="66.0769230769231" customWidth="1"/>
-    <col min="6" max="6" width="30.4423076923077" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="7.68269230769231" customWidth="1"/>
+    <col min="3" max="3" width="12.8173076923077" customWidth="1"/>
+    <col min="4" max="4" width="17.6153846153846" customWidth="1"/>
+    <col min="5" max="5" width="13.9326923076923" customWidth="1"/>
+    <col min="6" max="6" width="49.0769230769231" customWidth="1"/>
+    <col min="7" max="7" width="39.5384615384615" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="2" ht="20" customHeight="1" spans="2:8">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1">
+    <row r="3" ht="20" customHeight="1" spans="2:8">
+      <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G3" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1">
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="2:8">
+      <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="1"/>
+      <c r="F4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1"/>
+      <c r="G4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="2:8">
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="1"/>
+      <c r="F5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="2:8">
+      <c r="B6" s="1">
+        <v>4</v>
+      </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="1"/>
+      <c r="F6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="2:8">
+      <c r="B7" s="1">
+        <v>5</v>
+      </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="1"/>
+      <c r="F7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1">
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="2:8">
+      <c r="B8" s="1">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="2:8">
+      <c r="B9" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1">
+      <c r="F9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="2:8">
+      <c r="B10" s="1">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="2:8">
+      <c r="B11" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="2:8">
+      <c r="B12" s="1">
+        <v>10</v>
+      </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="1">
+      <c r="E12" s="1"/>
+      <c r="F12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="2:8">
+      <c r="B13" s="1">
+        <v>11</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="2:8">
+      <c r="B14" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="1">
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="2:8">
+      <c r="B15" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="1">
+      <c r="F15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="2:8">
+      <c r="B16" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="1">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="2:8">
+      <c r="B17" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="1">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="2:8">
+      <c r="B18" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="1">
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="2:8">
+      <c r="B19" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="7" t="s">
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="1">
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="2:8">
+      <c r="B20" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="2:8">
+      <c r="B21" s="1">
+        <v>19</v>
+      </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="1">
+      <c r="E21" s="1"/>
+      <c r="F21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="2:8">
+      <c r="B22" s="1">
+        <v>20</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="2:8">
+      <c r="B23" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="1"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="1">
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="F23" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="2:8">
+      <c r="B24" s="1">
+        <v>22</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="2:8">
+      <c r="B25" s="1">
         <v>23</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="1"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="1">
-        <v>23</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="C25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="1">
+      <c r="F25" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="2:8">
+      <c r="B26" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F25" s="1"/>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="1">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F26" s="1"/>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="1">
+      <c r="E26" s="1"/>
+      <c r="F26" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="2:8">
+      <c r="B27" s="1">
+        <v>25</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="2:8">
+      <c r="B28" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F27" s="1"/>
-    </row>
-    <row r="34" spans="6:6">
-      <c r="F34" s="8"/>
-    </row>
-    <row r="35" spans="6:6">
-      <c r="F35" s="8"/>
-    </row>
-    <row r="36" spans="6:6">
-      <c r="F36" s="8"/>
-    </row>
-    <row r="37" spans="6:6">
-      <c r="F37" s="8"/>
-    </row>
-    <row r="38" spans="6:6">
-      <c r="F38" s="8"/>
-    </row>
-    <row r="39" spans="6:6">
-      <c r="F39" s="8"/>
-    </row>
-    <row r="40" spans="6:6">
-      <c r="F40" s="8"/>
-    </row>
-    <row r="41" spans="6:6">
-      <c r="F41" s="6"/>
-    </row>
-    <row r="42" spans="6:6">
-      <c r="F42" s="6"/>
-    </row>
-    <row r="43" spans="2:5">
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-    </row>
-    <row r="44" spans="2:5">
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-    </row>
-    <row r="45" spans="2:5">
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-    </row>
-    <row r="46" spans="2:5">
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B2:B13"/>
-    <mergeCell ref="B14:B23"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="C2:C13"/>
-    <mergeCell ref="C14:C23"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="D2:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="D14:D18"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="F2:F13"/>
-    <mergeCell ref="F14:F23"/>
-    <mergeCell ref="F24:F27"/>
+    <mergeCell ref="C3:C14"/>
+    <mergeCell ref="C15:C24"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="D3:D14"/>
+    <mergeCell ref="D15:D24"/>
+    <mergeCell ref="D25:D28"/>
+    <mergeCell ref="E3:E8"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="E15:E19"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="H3:H14"/>
+    <mergeCell ref="H15:H24"/>
+    <mergeCell ref="H25:H28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1879,66 +1940,66 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C9" s="2"/>
     </row>
